--- a/data/describe/few_shot/final_summary/messages_country.xlsx
+++ b/data/describe/few_shot/final_summary/messages_country.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\input_final_summary\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D357351D-A089-401F-8DA9-E6DB1A6BEB06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE2F0E0-0B35-4CAA-A712-235CD7CF6222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51900" yWindow="3180" windowWidth="27195" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53295" yWindow="2295" windowWidth="22980" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>User</t>
   </si>
@@ -141,27 +141,36 @@
     <t>A spontaneous and cautious country tends to exhibit a general wariness, often showing less trust towards people of different religions, nationalities, and even strangers they encounter for the first time. Such a nation might also feel less secure in its neighborhoods and express a reduced desire for greater respect for authority in the future.</t>
   </si>
   <si>
-    <t xml:space="preserve">Now your task is to provide a description of a cluster.
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
+    <t>Fantastic! That’s exactly what I needed.
+Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. You will describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of the country: ```Brazil is average on engaged and faithful. Brazil is quite low on skeptical and autonomous. Brazil is quite low on group membership. Brazil is very low on systemic trust. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is very high on patriotic and disciplined. In particular, Brazil indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Brazil is quite high on vigilant and risk-aware. Brazil is very high on private and worldly. Brazil is quite low on content and accepting. Brazil is average on cooperative and open. ´´´ Here is the informative description of a country belongs to: ```Brazil is resilient guardian. The resilient guardian Brazil has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the country: ```Peru is very low on engaged and faithful. In particular, Peru indicates that Most people can be trusted (on a scale of 'most people can be trusted' to  'one needs to be very careful'). Peru is quite low on skeptical and autonomous. Peru is average on individual focus. Peru is very low on systemic trust. In particular, Peru indicates that How much confidence do you have in the government? (on a scale of ' a great deal' to 'none at all'). Peru is very high on patriotic and disciplined. In particular, Peru indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Peru is average on vigilant and risk-aware. Peru is average on private and worldly. Peru is quite low on content and accepting. Peru is very low on self-reliant and mindful. In particular, Peru indicates that In the future, would it be a good thing if we had greater respect for authority? (on a scale of 'good' to 'bad'). ´´´ 
+Here is the informative description of a country belongs to: ```Peru is resilient guardian. The resilient guardian Peru has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
+  </si>
+  <si>
+    <t>Peruvians stand out in their emphasis on survival values, viewing work as very important, possibly because it  plays central role in stability of daily life. Peruvians are skeptical toward political institutions, with many of them reporting no confidence in parliament. In other dimensions such as tradition versus secularism, neutrality, fairness, and tranquility, Peru aligns closely with the global average. Overall, Peruvian society appears deeply focused on survival and work, while remaining cautious and distrustful of formal political authority.</t>
+  </si>
+  <si>
+    <t>Brazil does not stand out strongly in any value dimension. Brazilians show no strong leanings toward either tradition or secularism, or toward survival or self-expression priorities.  The country’s value system mirrors international norms, with neutrality and outlook aligned with the global middle ground. Although individual Brazilian citizens might have a wide range of views, on the average they do not diverge significantly from worldwide patterns.</t>
+  </si>
+  <si>
+    <t>This cluster describes individuals who prioritize personal freedom and adaptable beliefs, often holding more traditional or aligned viewpoints, but demonstrate lower trust in civic institutions and reduced engagement in structured group activities.
+Their key strengths include a strong focus on individual priorities and autonomous choice, fostering personal freedom and an adaptable mindset, alongside a greater inclination towards traditional or aligned values.
+However, they exhibit weaknesses in their lower levels of civic and faithful trust, less participation in structured organizations, a less calm perspective regarding potential threats, and a reduced tendency to be ordered and accepting.</t>
+  </si>
+  <si>
+    <t>Thats really good. You truly understand the factors and names. 
+Now your task is to provide a description of a cluster.
+Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.For each cluster, write a concise summary based on the available information.
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. </t>
-  </si>
-  <si>
-    <t>Understood. Please provide the cluster descriptions.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: relatively low on civic and faithful trust, normal on independent thought, slightly low on structured participation, slightly high on individual priorities, relatively low on secular and unaligned, slightly low on calm perspective, relatively high on autonomous choice and flexible beliefs, normal on joyful and bright, slightly low on ordered and accepting```</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who prioritize personal freedom and adaptable beliefs, often holding more traditional or aligned viewpoints, but demonstrate lower trust in civic institutions and reduced engagement in structured group activities.
-Their key strengths include a strong focus on individual priorities and autonomous choice, fostering personal freedom and an adaptable mindset, alongside a greater inclination towards traditional or aligned values.
-However, they exhibit weaknesses in their lower levels of civic and faithful trust, less participation in structured organizations, a less calm perspective regarding potential threats, and a reduced tendency to be ordered and accepting.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: normal on security concerns and social openness, slightly high on contextual morality, relatively high on public expression and contentment, slightly high on individual priorities, slightly high on traditional and patriotic, slightly high on vigilant outlook, relatively low on group affiliation and home values, relatively high on joyful and bright, normal on ordered and accepting```</t>
+I will provided you with the cluster description and you will return the summary. 
+Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: relatively low on civic and faithful trust, normal on independent thought, slightly low on structured participation, slightly high on individual priorities, relatively low on secular and unaligned, slightly low on calm perspective, relatively high on autonomous choice and flexible beliefs, normal on joyful and bright, slightly low on ordered and accepting´´´</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: normal on security concerns and social openness, slightly high on contextual morality, relatively high on public expression and contentment, slightly high on individual priorities, slightly high on traditional and patriotic, slightly high on vigilant outlook, relatively low on group affiliation and home values, relatively high on joyful and bright, normal on ordered and accepting´´´</t>
   </si>
   <si>
     <t>This cluster encompasses patriotic and joyful individuals who are active in public expression, while maintaining a flexible view on morality and a vigilant outlook.
@@ -169,12 +178,12 @@
 However, a potential weakness lies in their contextual morality, which allows for situational ethical justifications, alongside a lower emphasis on group affiliations and instilling traditional home values.</t>
   </si>
   <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: quite high on security concerns and social openness, slightly low on independent thought, quite low on structured participation, normal on state assuredness, slightly high on traditional and patriotic, slightly low on calm perspective, normal on group affiliation and home values, slightly low on personal well-being and social harmony, relatively high on spontaneous and cautious```</t>
-  </si>
-  <si>
     <t>This cluster is characterized by a strong traditional and patriotic identity, yet grapples with significant security concerns and a cautious, less critically independent outlook.
 Their strengths lie in a pronounced national pride, a commitment to cultural heritage and social duty, and an average trust in core state institutions.
 However, they exhibit heightened anxieties about potential conflicts and job security, coupled with lower personal well-being, reduced participation in structured civic organizations, and a general wariness towards diverse groups and strangers, alongside a somewhat diminished independent critical thought.</t>
+  </si>
+  <si>
+    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: quite high on security concerns and social openness, slightly low on independent thought, quite low on structured participation, normal on state assuredness, slightly high on traditional and patriotic, slightly low on calm perspective, normal on group affiliation and home values, slightly low on personal well-being and social harmony, relatively high on spontaneous and cautious´´´</t>
   </si>
   <si>
     <t>Those were really good. Exactly what I am looking for. 
@@ -185,26 +194,12 @@
 The first sentence should give an overview of the cluster. 
 The second sentence should describe the cluster’s specific strengths based on the available information.
 The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  slightly low on civic and faithful trust,  normal on independent thought,  relatively high on public expression and contentment,  relatively low on state assuredness,  normal on traditional and patriotic,  slightly high on vigilant outlook,  normal on autonomous choice and flexible beliefs,  relatively low on personal well-being and social harmony,  normal on spontaneous and cautious```</t>
+Now do the same thing with the following: ```Members of this cluster can be described as:  slightly low on civic and faithful trust,  normal on independent thought,  relatively high on public expression and contentment,  relatively low on state assuredness,  normal on traditional and patriotic,  slightly high on vigilant outlook,  normal on autonomous choice and flexible beliefs,  relatively low on personal well-being and social harmony,  normal on spontaneous and cautious´´´</t>
   </si>
   <si>
     <t>This cluster represents a society that, while generally content and willing to express itself publicly, harbors a low level of trust in its state institutions and a cautious, slightly vigilant outlook.
 Its notable strengths include a relatively high public expression and contentment, indicating a populace that is both generally happy and inclined to make its voice heard, alongside an average capacity for independent thought.
 Weaknesses are evident in a relatively low state assuredness and civic trust, pointing to a lack of confidence in governing bodies and general interpersonal trust, compounded by a relatively low personal well-being and social harmony, and a slightly heightened sense of vigilance against potential threats.</t>
-  </si>
-  <si>
-    <t>Fantastic! That’s exactly what I needed.
-Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. You will describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of the country: ```Brazil is average on engaged and faithful. Brazil is quite low on skeptical and autonomous. Brazil is quite low on group membership. Brazil is very low on systemic trust. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is very high on patriotic and disciplined. In particular, Brazil indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Brazil is quite high on vigilant and risk-aware. Brazil is very high on private and worldly. Brazil is quite low on content and accepting. Brazil is average on cooperative and open. ´´´ Here is the informative description of a country belongs to: ```Brazil is resilient guardian. The resilient guardian Brazil has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of the country: ```Peru is very low on engaged and faithful. In particular, Peru indicates that Most people can be trusted (on a scale of 'most people can be trusted' to  'one needs to be very careful'). Peru is quite low on skeptical and autonomous. Peru is average on individual focus. Peru is very low on systemic trust. In particular, Peru indicates that How much confidence do you have in the government? (on a scale of ' a great deal' to 'none at all'). Peru is very high on patriotic and disciplined. In particular, Peru indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Peru is average on vigilant and risk-aware. Peru is average on private and worldly. Peru is quite low on content and accepting. Peru is very low on self-reliant and mindful. In particular, Peru indicates that In the future, would it be a good thing if we had greater respect for authority? (on a scale of 'good' to 'bad'). ´´´ 
-Here is the informative description of a country belongs to: ```Peru is resilient guardian. The resilient guardian Peru has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
-  </si>
-  <si>
-    <t>Peruvians stand out in their emphasis on survival values, viewing work as very important, possibly because it  plays central role in stability of daily life. Peruvians are skeptical toward political institutions, with many of them reporting no confidence in parliament. In other dimensions such as tradition versus secularism, neutrality, fairness, and tranquility, Peru aligns closely with the global average. Overall, Peruvian society appears deeply focused on survival and work, while remaining cautious and distrustful of formal political authority.</t>
-  </si>
-  <si>
-    <t>Brazil does not stand out strongly in any value dimension. Brazilians show no strong leanings toward either tradition or secularism, or toward survival or self-expression priorities.  The country’s value system mirrors international norms, with neutrality and outlook aligned with the global middle ground. Although individual Brazilian citizens might have a wide range of views, on the average they do not diverge significantly from worldwide patterns.</t>
   </si>
 </sst>
 </file>
@@ -570,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="83.453125" style="2" customWidth="1"/>
@@ -729,60 +724,52 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="232" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="348" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="145" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="232" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="348" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/final_summary/messages_country.xlsx
+++ b/data/describe/few_shot/final_summary/messages_country.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE2F0E0-0B35-4CAA-A712-235CD7CF6222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F9988C-0930-41D0-9A03-A82ADF5E9AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53295" yWindow="2295" windowWidth="22980" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="53295" yWindow="2640" windowWidth="23370" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>User</t>
   </si>
@@ -33,180 +33,186 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a country is described as civic and faithful trust?</t>
-  </si>
-  <si>
-    <t>A country exhibiting civic and faithful trust is one where its citizens are very willing to engage in political action, readily signing both traditional and electronic petitions. Here, a deep sense of faith is evident, with God holding significant importance, and there's a strong belief that most people, including those from other nationalities, can be trusted completely.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as security concerns and social openness?</t>
-  </si>
-  <si>
-    <t>A country characterized by 'security concerns and social openness' is often preoccupied with deep anxieties, grappling with the very real potential for civil war or a wider international conflict involving their nation. This is paired with concerns over citizens losing their jobs and providing children with a good education; furthermore, the extent to which abortion can be justified is a significant aspect of its social considerations.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as independent thought?</t>
-  </si>
-  <si>
-    <t>A country characterized by independent thought sees its citizens exhibiting a critical eye towards authority, with less confidence placed in their political parties, parliament, and government. This independent spirit also extends to their societal views, as they tend to believe that less importance should be placed on work in the future.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as contextual morality?</t>
-  </si>
-  <si>
-    <t>When a country is described as having contextual morality, it's one where the lines between right and wrong are not always clear-cut. This means that acts such as stealing, violence against others, accepting bribes, cheating on taxes, or even a man beating his wife might be seen as justifiable, depending on the specific circumstances.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as structured participation?</t>
-  </si>
-  <si>
-    <t>When a country is described as having structured participation, it means its citizens are very actively involved in charitable, humanitarian, and professional organizations. Furthermore, people in such a country frequently join self-help, mutual aid, and consumer organizations, demonstrating a strong commitment to collective engagement.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as public expression and contentment?</t>
-  </si>
-  <si>
-    <t>When a country is described as embracing public expression and contentment, it suggests its citizens have a slight inclination to make their voices heard by signing both electronic and traditional petitions. Beyond that, these are places where people tend to trust individuals of other religions and generally report feeling quite happy with their lives.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as state assuredness?</t>
-  </si>
-  <si>
-    <t>When a country is described as 'state assuredness,' it means its people hold a profound trust in their core political bodies, like the government, parliament, and political parties. This assurance extends deeply to the civil services and the justice system, reflecting a strong belief in their nation's institutional framework.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as individual priorities?</t>
-  </si>
-  <si>
-    <t>When a country is described by its individual priorities, it means that the idea of showing greater respect for authority doesn't quite resonate, and the importance of children learning obedience at home isn't highly stressed. Instead, people in such a nation genuinely cherish their personal leisure time.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as secular and unaligned?</t>
-  </si>
-  <si>
-    <t>When a country is described as secular and unaligned, it suggests a society that tends to distance itself from strict religious affiliations and traditional values. This means its citizens may not prioritize membership in various organizations, whether they are professional, charitable, or religious, and might view the importance of God in their lives as minimal.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as traditional and patriotic?</t>
-  </si>
-  <si>
-    <t>When a country is described as traditional and patriotic, it reflects a strong emphasis on cultural heritage and the importance of instilling religious values in children. Citizens often express pride in their nationality, view work as a social duty, and uphold traditional beliefs about societal roles, showcasing a commitment to their country’s values and history.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as calm perspective?</t>
-  </si>
-  <si>
-    <t>When a country is described as having a calm perspective, it reflects an absence of worry and anxiety about potential threats such as terrorist attacks or wars. Instead of fretting about uncertainties, this country approaches its existence with a sense of serenity and stability, embodying a tranquil mindset.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as vigilant outlook?</t>
-  </si>
-  <si>
-    <t>When a country is described as having a vigilant outlook, it reflects a sense of unease and concern regarding potential threats such as terrorism, war, or civil unrest. This country tends to harbor worries about safety and security, even if those worries may not be overwhelming.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as group affiliation and home values?</t>
-  </si>
-  <si>
-    <t>When a country is described as having group affiliation and home values, it emphasizes the importance of community and connection, including participation in professional and charitable organizations. Additionally, it suggests a focus on instilling religious values and teachings in the home, reflecting a collective identity and shared beliefs among its people.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as autonomous choice and flexible beliefs?</t>
-  </si>
-  <si>
-    <t>When a country is described as having autonomous choice and flexible beliefs, it embraces individuality and personal freedom over strong group ties or rigid traditions. This means that decision-making is more about personal preference rather than adhering strictly to collective norms or familial expectations, allowing for a more diverse and adaptable society.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as personal well-being and social harmony?</t>
-  </si>
-  <si>
-    <t>When a country is described as personal well-being and social harmony, it reflects a sense of life satisfaction among its people, indicating that individuals feel generally content with their lives. Additionally, this concept encompasses the levels of trust within communities and families, promoting social cohesion and a welcoming environment where diverse lifestyles can coexist peacefully.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as joyful and bright?</t>
-  </si>
-  <si>
-    <t>When a country is described as joyful and bright, it reflects a sense of happiness among its people, where individuals often feel happy about their lives. This positive vibe, although not strongly emphasized, hints at a community where moments of joy bring a sparkle to everyday living.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as ordered and accepting?</t>
-  </si>
-  <si>
-    <t>Countries described as ordered and accepting are those where citizens tend to embrace respect for authority and feel quite secure in their neighborhoods. These nations also show a remarkable openness, extending a good measure of trust to people of different religions, nationalities, and even those they encounter for the very first time.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as spontaneous and cautious?</t>
-  </si>
-  <si>
-    <t>A spontaneous and cautious country tends to exhibit a general wariness, often showing less trust towards people of different religions, nationalities, and even strangers they encounter for the first time. Such a nation might also feel less secure in its neighborhoods and express a reduced desire for greater respect for authority in the future.</t>
-  </si>
-  <si>
-    <t>Fantastic! That’s exactly what I needed.
-Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. You will describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of the country: ```Brazil is average on engaged and faithful. Brazil is quite low on skeptical and autonomous. Brazil is quite low on group membership. Brazil is very low on systemic trust. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is very high on patriotic and disciplined. In particular, Brazil indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Brazil is quite high on vigilant and risk-aware. Brazil is very high on private and worldly. Brazil is quite low on content and accepting. Brazil is average on cooperative and open. ´´´ Here is the informative description of a country belongs to: ```Brazil is resilient guardian. The resilient guardian Brazil has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of the country: ```Peru is very low on engaged and faithful. In particular, Peru indicates that Most people can be trusted (on a scale of 'most people can be trusted' to  'one needs to be very careful'). Peru is quite low on skeptical and autonomous. Peru is average on individual focus. Peru is very low on systemic trust. In particular, Peru indicates that How much confidence do you have in the government? (on a scale of ' a great deal' to 'none at all'). Peru is very high on patriotic and disciplined. In particular, Peru indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Peru is average on vigilant and risk-aware. Peru is average on private and worldly. Peru is quite low on content and accepting. Peru is very low on self-reliant and mindful. In particular, Peru indicates that In the future, would it be a good thing if we had greater respect for authority? (on a scale of 'good' to 'bad'). ´´´ 
-Here is the informative description of a country belongs to: ```Peru is resilient guardian. The resilient guardian Peru has the following characteristics: This cluster is characterized by individuals who exhibit a mix of patriotic and disciplined attitudes, while showing lower levels of engagement and systemic trust. Their strength lies in their vigilant and risk-aware mindset, along with a solid sense of discipline, indicating a capacity for responsibility and a proactive approach to challenges. However, this cluster has weaknesses in terms of lower engagement and a lack of contentment, which may hinder their ability to foster deeper social connections and collective wellbeing.´´´</t>
-  </si>
-  <si>
-    <t>Peruvians stand out in their emphasis on survival values, viewing work as very important, possibly because it  plays central role in stability of daily life. Peruvians are skeptical toward political institutions, with many of them reporting no confidence in parliament. In other dimensions such as tradition versus secularism, neutrality, fairness, and tranquility, Peru aligns closely with the global average. Overall, Peruvian society appears deeply focused on survival and work, while remaining cautious and distrustful of formal political authority.</t>
-  </si>
-  <si>
-    <t>Brazil does not stand out strongly in any value dimension. Brazilians show no strong leanings toward either tradition or secularism, or toward survival or self-expression priorities.  The country’s value system mirrors international norms, with neutrality and outlook aligned with the global middle ground. Although individual Brazilian citizens might have a wide range of views, on the average they do not diverge significantly from worldwide patterns.</t>
-  </si>
-  <si>
-    <t>This cluster describes individuals who prioritize personal freedom and adaptable beliefs, often holding more traditional or aligned viewpoints, but demonstrate lower trust in civic institutions and reduced engagement in structured group activities.
-Their key strengths include a strong focus on individual priorities and autonomous choice, fostering personal freedom and an adaptable mindset, alongside a greater inclination towards traditional or aligned values.
-However, they exhibit weaknesses in their lower levels of civic and faithful trust, less participation in structured organizations, a less calm perspective regarding potential threats, and a reduced tendency to be ordered and accepting.</t>
-  </si>
-  <si>
-    <t>Thats really good. You truly understand the factors and names. 
-Now your task is to provide a description of a cluster.
-Please use the statistical description enclosed with ``` ´´´ . It provides information about the cluster based on the latent factors that most accurately describe it.For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-I will provided you with the cluster description and you will return the summary. 
-Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: relatively low on civic and faithful trust, normal on independent thought, slightly low on structured participation, slightly high on individual priorities, relatively low on secular and unaligned, slightly low on calm perspective, relatively high on autonomous choice and flexible beliefs, normal on joyful and bright, slightly low on ordered and accepting´´´</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: normal on security concerns and social openness, slightly high on contextual morality, relatively high on public expression and contentment, slightly high on individual priorities, slightly high on traditional and patriotic, slightly high on vigilant outlook, relatively low on group affiliation and home values, relatively high on joyful and bright, normal on ordered and accepting´´´</t>
-  </si>
-  <si>
-    <t>This cluster encompasses patriotic and joyful individuals who are active in public expression, while maintaining a flexible view on morality and a vigilant outlook.
-Their strengths include a strong sense of national pride, high levels of personal happiness and contentment, an inclination for public expression, and a valuable awareness of potential threats.
-However, a potential weakness lies in their contextual morality, which allows for situational ethical justifications, alongside a lower emphasis on group affiliations and instilling traditional home values.</t>
-  </si>
-  <si>
-    <t>This cluster is characterized by a strong traditional and patriotic identity, yet grapples with significant security concerns and a cautious, less critically independent outlook.
-Their strengths lie in a pronounced national pride, a commitment to cultural heritage and social duty, and an average trust in core state institutions.
-However, they exhibit heightened anxieties about potential conflicts and job security, coupled with lower personal well-being, reduced participation in structured civic organizations, and a general wariness towards diverse groups and strangers, alongside a somewhat diminished independent critical thought.</t>
-  </si>
-  <si>
-    <t>Here is the cluster description based on the factor scores at the cluster center, representing a typical country in that cluster:```Members of this cluster can be described as: quite high on security concerns and social openness, slightly low on independent thought, quite low on structured participation, normal on state assuredness, slightly high on traditional and patriotic, slightly low on calm perspective, normal on group affiliation and home values, slightly low on personal well-being and social harmony, relatively high on spontaneous and cautious´´´</t>
-  </si>
-  <si>
-    <t>Those were really good. Exactly what I am looking for. 
-Make sure you continue to use the same format and style in the next example. 
-I am now going to give you one last description task to complete. 
-You will receive information about the cluster based on the latent factors that best describe it.
-For each cluster, write a concise summary based on the available information.
-The first sentence should give an overview of the cluster. 
-The second sentence should describe the cluster’s specific strengths based on the available information.
-The third sentence should highlight areas where the cluster has specific weaknesses based on the available information.
-Now do the same thing with the following: ```Members of this cluster can be described as:  slightly low on civic and faithful trust,  normal on independent thought,  relatively high on public expression and contentment,  relatively low on state assuredness,  normal on traditional and patriotic,  slightly high on vigilant outlook,  normal on autonomous choice and flexible beliefs,  relatively low on personal well-being and social harmony,  normal on spontaneous and cautious´´´</t>
-  </si>
-  <si>
-    <t>This cluster represents a society that, while generally content and willing to express itself publicly, harbors a low level of trust in its state institutions and a cautious, slightly vigilant outlook.
-Its notable strengths include a relatively high public expression and contentment, indicating a populace that is both generally happy and inclined to make its voice heard, alongside an average capacity for independent thought.
-Weaknesses are evident in a relatively low state assuredness and civic trust, pointing to a lack of confidence in governing bodies and general interpersonal trust, compounded by a relatively low personal well-being and social harmony, and a slightly heightened sense of vigilance against potential threats.</t>
+    <t>What does it mean when a country is described as confident and engaged?</t>
+  </si>
+  <si>
+    <t>When a country is described as confident and engaged, it showcases a spirit of active participation and trust among its citizens. People are likely to view political engagement, like signing electronic petitions, as a positive action, and they tend to have a strong belief in the importance of faith, while also trusting others, including those from different nationalities. This creates a vibrant atmosphere where individuals feel empowered and connected to one another and their governance.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as concerned and cautious?</t>
+  </si>
+  <si>
+    <t>When a country is described as concerned and cautious, it indicates a deep sense of worry about various critical issues. This includes significant fears about providing quality education for future generations, anxieties over potential civil conflict and war, and worries about job security and employment prospects. Overall, such a country tends to approach situations with a careful and apprehensive mindset, reflecting a desire to protect its citizens from uncertainty and challenges.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as principled?</t>
+  </si>
+  <si>
+    <t>When a country is described as principled, it indicates that there is a measured level of confidence in its political structures, such as political parties, parliament, and government, even if that confidence is not overwhelmingly high. This suggests that the country values integrity and has a sense of ethical responsibility in its governance, contrasting sharply with a lack of concern for moral standards.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as indifferent?</t>
+  </si>
+  <si>
+    <t>When a country is described as indifferent, it means that there is a troubling ease with which certain behaviors, such as stealing, violence, accepting bribes, domestic abuse, and tax cheating, can be justified. This reflects a lack of ethical conviction where right and wrong become blurred, indicating a society that may turn a blind eye to moral transgressions.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as active and involved?</t>
+  </si>
+  <si>
+    <t>When a country is described as active and involved, it means that its citizens actively participate in various organizations, such as charitable or professional groups, showing a strong commitment to community engagement. This enthusiasm extends to support for self-help or consumer organizations, highlighting a vibrant participation that fosters connections and collective action.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as passive and distant?</t>
+  </si>
+  <si>
+    <t>When a country is described as passive and distant, it suggests a lack of engagement and reluctance to take action on significant issues. People in such a country may be less likely to participate in petitions or political actions, exhibit a general distrust towards those of different backgrounds, and report feelings of unhappiness, reflecting a disengaged and aloof society.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as trusted?</t>
+  </si>
+  <si>
+    <t>When a country is described as trusted, it indicates a strong sense of confidence that its government, parliament, political parties, civil services, and justice system can be relied upon. This trust reflects a belief that these institutions operate effectively and with integrity, fostering a sense of security and assurance among the citizens.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as skeptical?</t>
+  </si>
+  <si>
+    <t>When a country is described as skeptical, it reflects a general uncertainty about traditional authority and the importance placed on obedience, respect, and leisure time. This means that residents may question whether greater respect for authority is a positive step, showcasing a cautious outlook towards established power structures and values in society.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as involved and committed?</t>
+  </si>
+  <si>
+    <t>When a country is described as involved and committed, it reflects a community where citizens actively participate in various organizations, from professional and consumer groups to charitable and self-help initiatives. Additionally, thereâ€™s a sense of personal significance placed on beliefs and values, highlighting a connection to the role of faith in their lives. This involvement indicates a vibrant social fabric, where individuals care about their contributions and the welfare of their society.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as disengaged and indifferent?</t>
+  </si>
+  <si>
+    <t>When a country is described as disengaged and indifferent, it reflects a lack of connection and commitment to community and societal values. Citizens may not prioritize instilling religious faith in children, feel little pride in their nationality, and show skepticism towards the role of work in contributing to society, leading to an overall sense of disinterest and detachment from important aspects of a shared national identity.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as unworried?</t>
+  </si>
+  <si>
+    <t>When a country is described as unworried, it means that the nation does not have significant concerns about various threats, such as terrorist attacks, war, or civil unrest. In essence, this country exhibits a sense of calmness, free from the anxieties that might plague others regarding safety and security.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as anxious and fearful?</t>
+  </si>
+  <si>
+    <t>When a country is described as anxious and fearful, it reflects a sense of unease and concern about potential threats. Citizens may express worries about serious issues, such as the possibility of a terrorist attack, an impending war, or even a civil war, indicating that there is a prevailing atmosphere of apprehension and dread within the nation.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as participative and engaged?</t>
+  </si>
+  <si>
+    <t>When a country is described as participative and engaged, it means that its citizens tend to be involved in various organizations, such as professional and charitable groups, showing a willingness to contribute to society. Additionally, they value the importance of passing on religious beliefs to the next generation, reflecting an active engagement in both community and family values.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as not participative?</t>
+  </si>
+  <si>
+    <t>When a country is described as not participative, it suggests a lack of involvement in organizations and community activities. Citizens are not actively engaging in professional, charitable, or even spiritual realms, indicating a general disinterest in collaborative efforts and civic responsibility.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as satisfied and secure?</t>
+  </si>
+  <si>
+    <t>When a country is described as satisfied and secure, it reflects a sense of contentment and stability among its people. This can be seen in moderate life satisfaction levels, where individuals generally feel pleased with their lives, alongside a general trust in their neighborhoods and families, indicating a community that feels united and dependable.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as uncertain and hesitant?</t>
+  </si>
+  <si>
+    <t>When a country is described as uncertain and hesitant, it reflects a state of indecision and doubt about its overall happiness and contentment. This uncertainty suggests that citizens may struggle to feel truly joyful or confident in their circumstances, presenting a landscape where satisfaction is elusive.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as trusting?</t>
+  </si>
+  <si>
+    <t>When a country is described as trusting, it reflects a general belief in the goodness of others, as seen in the way its citizens feel secure in their neighborhoods and are open to trusting people from different religions and nationalities. This sense of trust also extends to new acquaintances, suggesting a welcoming spirit and confidence in relationships with others.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as mistrusting?</t>
+  </si>
+  <si>
+    <t>When a country is described as mistrusting, it means that its people tend to not trust others easily, whether it involves new acquaintances, those from different religions, or individuals of varying nationalities. This lack of trust can create an atmosphere of skepticism and uncertainty, where people are cautious and hesitant to engage with others fully.</t>
+  </si>
+  <si>
+    <t>This cluster characterizes countries that display a general sense of disengagement and anxiety in their societal dynamics. Despite being principled and maintaining a degree of participation, these countries struggle with lower levels of trust and satisfaction, suggesting a community that is not fully confident in its engagement. The notable weaknesses in this cluster lie in their high levels of anxiety and fearfulness, combined with a tendency towards disengagement and indifference, which may hinder progress and collaboration among their citizens.</t>
+  </si>
+  <si>
+    <t>This cluster represents countries that exhibit a reserved approach towards engagement and commitment, characterized by a noticeable lack of confidence and proactivity. Specific strengths include a principled stance on issues and a stable score on participative engagement, suggesting a balanced approach to civic involvement when prompted. However, the cluster faces weaknesses in its skepticism, low levels of active participation, and a tendency toward uncertainty, which may hinder effective collaboration and positive progress on relevant social issues.</t>
+  </si>
+  <si>
+    <t>This cluster represents countries characterized by a cautious and somewhat disengaged demeanor. The members of this cluster display a notable strength in their awareness of potential risks, as indicated by their high levels of concern and skepticism, alongside a pronounced anxiety about their circumstances. However, their specific weaknesses lie in their low levels of trust and participation, which may hinder their ability to effectively address challenges and foster a sense of community engagement.</t>
+  </si>
+  <si>
+    <t>This cluster represents a group characterized by a tendency towards disengagement and distance. Members exhibit a notable level of caution and trust, but their hesitance and passivity indicate a lack of proactive involvement in various matters. The primary weakness of this cluster lies in its high levels of uncertainty and disengagement, which may hinder effective collaboration and responsiveness in dynamic environments.</t>
+  </si>
+  <si>
+    <t>This cluster consists of countries that display a notable degree of concern and caution, reflecting a reserved approach to engagement. The strengths of this cluster include a structured perspective that often results in careful deliberation on issues, though this cautiousness may also foster a sense of indifference in their response to various initiatives. However, the specific weaknesses of this cluster lie in their low levels of participation and trust, indicating a potential challenge in fostering committed and collaborative relationships both domestically and internationally.</t>
+  </si>
+  <si>
+    <t>This cluster represents a group of countries showcasing a significant level of indifference and skepticism, reflecting a low commitment to civic engagement. Their specific strengths lie in a high degree of passive observation and express skepticism about participatory initiatives, highlighting a tendency to critically assess their environments. However, this cluster faces notable weaknesses, such as low levels of satisfaction and security, an overwhelming sense of mistrust, and a disengaged outlook that may hinder social cohesion and progress.</t>
+  </si>
+  <si>
+    <t>Members of this cluster exhibit a predominant tendency towards concern and caution, suggesting a heightened sensitivity to risks and uncertainties. Their skepticism and disengagement may reflect a lack of active involvement in societal matters, paired with a significant mistrust in external systems or institutions. However, this cluster also shows vulnerabilities, particularly in their lower levels of satisfaction and security, which may hinder their overall confidence and engagement in various aspects of life.</t>
+  </si>
+  <si>
+    <t>This cluster represents countries characterized by a significant lack of confidence and engagement, which results in a cautious and hesitant outlook. A specific strength of this cluster is that while they are reasonably trusted, they struggle with high levels of uncertainty and mistrust towards other entities. The notable weakness lies in their very low levels of participation and commitment, coupled with a marked tendency to remain passive and distant, leading to challenges in fostering proactive governance and societal involvement.</t>
+  </si>
+  <si>
+    <t>This cluster depicts a group characterized by a generally cautious approach, coupled with a slight tendency towards skepticism and passivity. Their notable strengths lie in their satisfaction and security, alongside a balanced outlook, implying some stability in their perspective. However, the cluster struggles with low levels of principled actions, involvement, and trust, which may hinder their progress and engagement with broader societal issues.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as supportive haven?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as balanced insight?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as prudent observer?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as calm observer?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as thoughtful guardian?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as observant skeptic?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as cautious thinker?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as reserved confidence?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as secure skeptic?</t>
+  </si>
+  <si>
+    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of the country: ```Brazil is average on confident and engaged. Brazil is quite low on principled. Brazil is quite low on active and involved. Brazil is very low on trusted. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is very high on disengaged and indifferent. In particular, Brazil indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Brazil is quite high on anxious and fearful. Brazil is very high on not participative. Brazil is quite low on satisfied and secure. Brazil is average on mistrusting. ´´´ Here is the informative description of a country belongs to: ```Brazil is supportive haven with the following characteristics: This cluster characterizes countries that display a general sense of disengagement and anxiety in their societal dynamics. Despite being principled and maintaining a degree of participation, these countries struggle with lower levels of trust and satisfaction, suggesting a community that is not fully confident in its engagement. The notable weaknesses in this cluster lie in their high levels of anxiety and fearfulness, combined with a tendency towards disengagement and indifference, which may hinder progress and collaboration among their citizens.´´´</t>
+  </si>
+  <si>
+    <t>Brazil can be characterized as a country experiencing significant disengagement and anxiety within its societal framework. Its specific strengths include a normal level of confidence and engagement, albeit accompanied by a pronounced lack of trust in institutions like the justice system. However, Brazil shows weaknesses in participation and satisfaction, and its citizens exhibit a higher tendency towards anxiety and indifference, reflecting a lack of overall confidence. In summary, Brazil represents a supportive haven, where the combination of low trust and high anxiety may impede societal cohesion and progress.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of the country: ```Peru is very low on confident and engaged. In particular, Peru indicates that Most people can be trusted (on a scale of 'most people can be trusted' to  'one needs to be very careful'). Peru is quite low on principled. Peru is average on passive and distant. Peru is very low on trusted. In particular, Peru indicates that How much confidence do you have in the government? (on a scale of ' a great deal' to 'none at all'). Peru is very high on disengaged and indifferent. In particular, Peru indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Peru is average on anxious and fearful. Peru is average on not participative. Peru is quite low on satisfied and secure. Peru is very low on trusting. In particular, Peru indicates that In the future, would it be a good thing if we had greater respect for authority? (on a scale of 'good' to 'bad'). ´´´ 
+Here is the informative description of a country belongs to: ```Peru is supportive haven with the following characteristics: This cluster characterizes countries that display a general sense of disengagement and anxiety in their societal dynamics. Despite being principled and maintaining a degree of participation, these countries struggle with lower levels of trust and satisfaction, suggesting a community that is not fully confident in its engagement. The notable weaknesses in this cluster lie in their high levels of anxiety and fearfulness, combined with a tendency towards disengagement and indifference, which may hinder progress and collaboration among their citizens.´´´</t>
+  </si>
+  <si>
+    <t>Peru can be characterized as a supportive haven, demonstrating a marked disengagement from societal engagement and a pervasive sense of anxiety. The country showcases a principled stance while maintaining a degree of participation, yet it suffers from low levels of trust, indicating a community that struggles to fully engage. Moreover, Peru displays average levels of anxiousness and passivity, coupled with significant weakness in overall satisfaction and trust, which hinders the potential for collaboration and progress among its citizens. In summary, while Peru possesses some foundational principles, its prevalent disengagement and skepticism reveal a need for enhanced civic engagement and community trust.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,20 +221,321 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -237,38 +544,215 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -291,44 +775,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -355,14 +839,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -389,6 +891,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -400,176 +920,152 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="83.453125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="94" style="2" customWidth="1"/>
+    <col min="1" max="1" width="88.54296875" customWidth="1"/>
+    <col min="2" max="2" width="103.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -580,7 +1076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -588,7 +1084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -596,7 +1092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -604,7 +1100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -612,7 +1108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -620,7 +1116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -628,7 +1124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -636,7 +1132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -644,7 +1140,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -652,7 +1148,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -660,7 +1156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="21.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -668,7 +1164,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -676,7 +1172,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -684,7 +1180,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="21.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -692,7 +1188,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
@@ -700,7 +1196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" ht="21.5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -708,7 +1204,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -716,7 +1212,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
@@ -724,56 +1220,96 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="2" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="28" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="232" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="348" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>40</v>
+    <row r="29" spans="1:2" ht="150" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="130" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/describe/few_shot/final_summary/messages_country.xlsx
+++ b/data/describe/few_shot/final_summary/messages_country.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F9988C-0930-41D0-9A03-A82ADF5E9AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F61F11C-81CD-4028-9D84-329B9F14C028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53295" yWindow="2640" windowWidth="23370" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="QandA_data" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>User</t>
   </si>
@@ -33,186 +33,91 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a country is described as confident and engaged?</t>
-  </si>
-  <si>
-    <t>When a country is described as confident and engaged, it showcases a spirit of active participation and trust among its citizens. People are likely to view political engagement, like signing electronic petitions, as a positive action, and they tend to have a strong belief in the importance of faith, while also trusting others, including those from different nationalities. This creates a vibrant atmosphere where individuals feel empowered and connected to one another and their governance.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as concerned and cautious?</t>
-  </si>
-  <si>
-    <t>When a country is described as concerned and cautious, it indicates a deep sense of worry about various critical issues. This includes significant fears about providing quality education for future generations, anxieties over potential civil conflict and war, and worries about job security and employment prospects. Overall, such a country tends to approach situations with a careful and apprehensive mindset, reflecting a desire to protect its citizens from uncertainty and challenges.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as principled?</t>
-  </si>
-  <si>
-    <t>When a country is described as principled, it indicates that there is a measured level of confidence in its political structures, such as political parties, parliament, and government, even if that confidence is not overwhelmingly high. This suggests that the country values integrity and has a sense of ethical responsibility in its governance, contrasting sharply with a lack of concern for moral standards.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as indifferent?</t>
-  </si>
-  <si>
-    <t>When a country is described as indifferent, it means that there is a troubling ease with which certain behaviors, such as stealing, violence, accepting bribes, domestic abuse, and tax cheating, can be justified. This reflects a lack of ethical conviction where right and wrong become blurred, indicating a society that may turn a blind eye to moral transgressions.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as active and involved?</t>
-  </si>
-  <si>
-    <t>When a country is described as active and involved, it means that its citizens actively participate in various organizations, such as charitable or professional groups, showing a strong commitment to community engagement. This enthusiasm extends to support for self-help or consumer organizations, highlighting a vibrant participation that fosters connections and collective action.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as passive and distant?</t>
-  </si>
-  <si>
-    <t>When a country is described as passive and distant, it suggests a lack of engagement and reluctance to take action on significant issues. People in such a country may be less likely to participate in petitions or political actions, exhibit a general distrust towards those of different backgrounds, and report feelings of unhappiness, reflecting a disengaged and aloof society.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as trusted?</t>
-  </si>
-  <si>
-    <t>When a country is described as trusted, it indicates a strong sense of confidence that its government, parliament, political parties, civil services, and justice system can be relied upon. This trust reflects a belief that these institutions operate effectively and with integrity, fostering a sense of security and assurance among the citizens.</t>
+    <t>What does it mean when a country is described as unconfident?</t>
+  </si>
+  <si>
+    <t>When a country is described as unconfident, it reflects a sense of hesitancy or doubt about its political institutions, such as a weak confidence in political parties and parliament. This feeling extends to social values, where there might be uncertainty about the implications of prioritizing personal well-being over work, indicating a lack of assurance in the nationâ€™s collective direction and decisions.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as justifiable?</t>
+  </si>
+  <si>
+    <t>When a country is described as justifiable, it reflects a perspective where actions like stealing property, violence against others, accepting bribes, domestic abuse, and cheating on taxes are viewed through a lens of acceptability, suggesting that there are situations where these behaviors might seem reasonable or warranted. This stance encompasses a belief system that frequently justifies morally questionable actions, contributing to a broader understanding of social norms and ethics within that country.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as trusting?</t>
+  </si>
+  <si>
+    <t>When a country is described as trusting, it reflects a belief that most people can be relied upon and that there is a strong sense of confidence in both personal relationships and those across national boundaries. This trust extends beyond just individuals, highlighting the importance of faith in God and an openness to engage in political actions, such as signing electronic petitions, indicating a society that values cooperation and connection.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as concerned?</t>
+  </si>
+  <si>
+    <t>When a country is described as concerned, it means that its citizens are deeply troubled by various social issues and potential threats. They worry significantly about matters like education for future generations, the justifiability of abortion and homosexuality, and even the looming fear of civil unrest, indicating a collective anxiety about the moral and societal direction of their nation.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as confident?</t>
+  </si>
+  <si>
+    <t>When a country is described as confident, it means that its citizens have a strong trust in their government, parliament, and civil service, feeling secure in the systems that govern their lives. This confidence extends notably to their justice system and political parties, suggesting a robust belief in the overall integrity and effectiveness of their institutions.</t>
   </si>
   <si>
     <t>What does it mean when a country is described as skeptical?</t>
   </si>
   <si>
-    <t>When a country is described as skeptical, it reflects a general uncertainty about traditional authority and the importance placed on obedience, respect, and leisure time. This means that residents may question whether greater respect for authority is a positive step, showcasing a cautious outlook towards established power structures and values in society.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as involved and committed?</t>
-  </si>
-  <si>
-    <t>When a country is described as involved and committed, it reflects a community where citizens actively participate in various organizations, from professional and consumer groups to charitable and self-help initiatives. Additionally, thereâ€™s a sense of personal significance placed on beliefs and values, highlighting a connection to the role of faith in their lives. This involvement indicates a vibrant social fabric, where individuals care about their contributions and the welfare of their society.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as disengaged and indifferent?</t>
-  </si>
-  <si>
-    <t>When a country is described as disengaged and indifferent, it reflects a lack of connection and commitment to community and societal values. Citizens may not prioritize instilling religious faith in children, feel little pride in their nationality, and show skepticism towards the role of work in contributing to society, leading to an overall sense of disinterest and detachment from important aspects of a shared national identity.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as unworried?</t>
-  </si>
-  <si>
-    <t>When a country is described as unworried, it means that the nation does not have significant concerns about various threats, such as terrorist attacks, war, or civil unrest. In essence, this country exhibits a sense of calmness, free from the anxieties that might plague others regarding safety and security.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as anxious and fearful?</t>
-  </si>
-  <si>
-    <t>When a country is described as anxious and fearful, it reflects a sense of unease and concern about potential threats. Citizens may express worries about serious issues, such as the possibility of a terrorist attack, an impending war, or even a civil war, indicating that there is a prevailing atmosphere of apprehension and dread within the nation.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as participative and engaged?</t>
-  </si>
-  <si>
-    <t>When a country is described as participative and engaged, it means that its citizens tend to be involved in various organizations, such as professional and charitable groups, showing a willingness to contribute to society. Additionally, they value the importance of passing on religious beliefs to the next generation, reflecting an active engagement in both community and family values.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as not participative?</t>
-  </si>
-  <si>
-    <t>When a country is described as not participative, it suggests a lack of involvement in organizations and community activities. Citizens are not actively engaging in professional, charitable, or even spiritual realms, indicating a general disinterest in collaborative efforts and civic responsibility.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as satisfied and secure?</t>
-  </si>
-  <si>
-    <t>When a country is described as satisfied and secure, it reflects a sense of contentment and stability among its people. This can be seen in moderate life satisfaction levels, where individuals generally feel pleased with their lives, alongside a general trust in their neighborhoods and families, indicating a community that feels united and dependable.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as uncertain and hesitant?</t>
-  </si>
-  <si>
-    <t>When a country is described as uncertain and hesitant, it reflects a state of indecision and doubt about its overall happiness and contentment. This uncertainty suggests that citizens may struggle to feel truly joyful or confident in their circumstances, presenting a landscape where satisfaction is elusive.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as trusting?</t>
-  </si>
-  <si>
-    <t>When a country is described as trusting, it reflects a general belief in the goodness of others, as seen in the way its citizens feel secure in their neighborhoods and are open to trusting people from different religions and nationalities. This sense of trust also extends to new acquaintances, suggesting a welcoming spirit and confidence in relationships with others.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as mistrusting?</t>
-  </si>
-  <si>
-    <t>When a country is described as mistrusting, it means that its people tend to not trust others easily, whether it involves new acquaintances, those from different religions, or individuals of varying nationalities. This lack of trust can create an atmosphere of skepticism and uncertainty, where people are cautious and hesitant to engage with others fully.</t>
-  </si>
-  <si>
-    <t>This cluster characterizes countries that display a general sense of disengagement and anxiety in their societal dynamics. Despite being principled and maintaining a degree of participation, these countries struggle with lower levels of trust and satisfaction, suggesting a community that is not fully confident in its engagement. The notable weaknesses in this cluster lie in their high levels of anxiety and fearfulness, combined with a tendency towards disengagement and indifference, which may hinder progress and collaboration among their citizens.</t>
-  </si>
-  <si>
-    <t>This cluster represents countries that exhibit a reserved approach towards engagement and commitment, characterized by a noticeable lack of confidence and proactivity. Specific strengths include a principled stance on issues and a stable score on participative engagement, suggesting a balanced approach to civic involvement when prompted. However, the cluster faces weaknesses in its skepticism, low levels of active participation, and a tendency toward uncertainty, which may hinder effective collaboration and positive progress on relevant social issues.</t>
-  </si>
-  <si>
-    <t>This cluster represents countries characterized by a cautious and somewhat disengaged demeanor. The members of this cluster display a notable strength in their awareness of potential risks, as indicated by their high levels of concern and skepticism, alongside a pronounced anxiety about their circumstances. However, their specific weaknesses lie in their low levels of trust and participation, which may hinder their ability to effectively address challenges and foster a sense of community engagement.</t>
-  </si>
-  <si>
-    <t>This cluster represents a group characterized by a tendency towards disengagement and distance. Members exhibit a notable level of caution and trust, but their hesitance and passivity indicate a lack of proactive involvement in various matters. The primary weakness of this cluster lies in its high levels of uncertainty and disengagement, which may hinder effective collaboration and responsiveness in dynamic environments.</t>
-  </si>
-  <si>
-    <t>This cluster consists of countries that display a notable degree of concern and caution, reflecting a reserved approach to engagement. The strengths of this cluster include a structured perspective that often results in careful deliberation on issues, though this cautiousness may also foster a sense of indifference in their response to various initiatives. However, the specific weaknesses of this cluster lie in their low levels of participation and trust, indicating a potential challenge in fostering committed and collaborative relationships both domestically and internationally.</t>
-  </si>
-  <si>
-    <t>This cluster represents a group of countries showcasing a significant level of indifference and skepticism, reflecting a low commitment to civic engagement. Their specific strengths lie in a high degree of passive observation and express skepticism about participatory initiatives, highlighting a tendency to critically assess their environments. However, this cluster faces notable weaknesses, such as low levels of satisfaction and security, an overwhelming sense of mistrust, and a disengaged outlook that may hinder social cohesion and progress.</t>
-  </si>
-  <si>
-    <t>Members of this cluster exhibit a predominant tendency towards concern and caution, suggesting a heightened sensitivity to risks and uncertainties. Their skepticism and disengagement may reflect a lack of active involvement in societal matters, paired with a significant mistrust in external systems or institutions. However, this cluster also shows vulnerabilities, particularly in their lower levels of satisfaction and security, which may hinder their overall confidence and engagement in various aspects of life.</t>
-  </si>
-  <si>
-    <t>This cluster represents countries characterized by a significant lack of confidence and engagement, which results in a cautious and hesitant outlook. A specific strength of this cluster is that while they are reasonably trusted, they struggle with high levels of uncertainty and mistrust towards other entities. The notable weakness lies in their very low levels of participation and commitment, coupled with a marked tendency to remain passive and distant, leading to challenges in fostering proactive governance and societal involvement.</t>
-  </si>
-  <si>
-    <t>This cluster depicts a group characterized by a generally cautious approach, coupled with a slight tendency towards skepticism and passivity. Their notable strengths lie in their satisfaction and security, alongside a balanced outlook, implying some stability in their perspective. However, the cluster struggles with low levels of principled actions, involvement, and trust, which may hinder their progress and engagement with broader societal issues.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as supportive haven?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as balanced insight?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as prudent observer?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as calm observer?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as thoughtful guardian?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as observant skeptic?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as cautious thinker?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as reserved confidence?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as secure skeptic?</t>
-  </si>
-  <si>
-    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of the country: ```Brazil is average on confident and engaged. Brazil is quite low on principled. Brazil is quite low on active and involved. Brazil is very low on trusted. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is very high on disengaged and indifferent. In particular, Brazil indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Brazil is quite high on anxious and fearful. Brazil is very high on not participative. Brazil is quite low on satisfied and secure. Brazil is average on mistrusting. ´´´ Here is the informative description of a country belongs to: ```Brazil is supportive haven with the following characteristics: This cluster characterizes countries that display a general sense of disengagement and anxiety in their societal dynamics. Despite being principled and maintaining a degree of participation, these countries struggle with lower levels of trust and satisfaction, suggesting a community that is not fully confident in its engagement. The notable weaknesses in this cluster lie in their high levels of anxiety and fearfulness, combined with a tendency towards disengagement and indifference, which may hinder progress and collaboration among their citizens.´´´</t>
-  </si>
-  <si>
-    <t>Brazil can be characterized as a country experiencing significant disengagement and anxiety within its societal framework. Its specific strengths include a normal level of confidence and engagement, albeit accompanied by a pronounced lack of trust in institutions like the justice system. However, Brazil shows weaknesses in participation and satisfaction, and its citizens exhibit a higher tendency towards anxiety and indifference, reflecting a lack of overall confidence. In summary, Brazil represents a supportive haven, where the combination of low trust and high anxiety may impede societal cohesion and progress.</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of the country: ```Peru is very low on confident and engaged. In particular, Peru indicates that Most people can be trusted (on a scale of 'most people can be trusted' to  'one needs to be very careful'). Peru is quite low on principled. Peru is average on passive and distant. Peru is very low on trusted. In particular, Peru indicates that How much confidence do you have in the government? (on a scale of ' a great deal' to 'none at all'). Peru is very high on disengaged and indifferent. In particular, Peru indicates that Do you think homosexuality can always be justified, never be justified, or something in between? (on a scale of 'never justifiable' to 'always justifiable'). Peru is average on anxious and fearful. Peru is average on not participative. Peru is quite low on satisfied and secure. Peru is very low on trusting. In particular, Peru indicates that In the future, would it be a good thing if we had greater respect for authority? (on a scale of 'good' to 'bad'). ´´´ 
-Here is the informative description of a country belongs to: ```Peru is supportive haven with the following characteristics: This cluster characterizes countries that display a general sense of disengagement and anxiety in their societal dynamics. Despite being principled and maintaining a degree of participation, these countries struggle with lower levels of trust and satisfaction, suggesting a community that is not fully confident in its engagement. The notable weaknesses in this cluster lie in their high levels of anxiety and fearfulness, combined with a tendency towards disengagement and indifference, which may hinder progress and collaboration among their citizens.´´´</t>
-  </si>
-  <si>
-    <t>Peru can be characterized as a supportive haven, demonstrating a marked disengagement from societal engagement and a pervasive sense of anxiety. The country showcases a principled stance while maintaining a degree of participation, yet it suffers from low levels of trust, indicating a community that struggles to fully engage. Moreover, Peru displays average levels of anxiousness and passivity, coupled with significant weakness in overall satisfaction and trust, which hinders the potential for collaboration and progress among its citizens. In summary, while Peru possesses some foundational principles, its prevalent disengagement and skepticism reveal a need for enhanced civic engagement and community trust.</t>
+    <t>When a country is described as skeptical, it conveys a sense of hesitation or doubt regarding certain activities and beliefs. This skepticism is reflected in the lower importance placed on leisure time and a reluctance toward participating in actions like signing petitions, suggesting a general caution or disbelief in the effectiveness or value of such engagements.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as active?</t>
+  </si>
+  <si>
+    <t>When a country is described as active, it means that its citizens are significantly engaged in professional, charitable, and consumer organizations, showing a commitment to community and collaboration. This vibrant participation reflects a society that values involvement and cooperation, often leading to a diverse range of initiatives that enhance social ties and support among individuals.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as passive?</t>
+  </si>
+  <si>
+    <t>When a country is described as passive, it suggests a tendency to shy away from active participation in political engagement, such as signing electronic petitions or taking community initiatives. This passivity reflects a reluctance to engage in actions that drive societal change, indicating a more subdued presence in active civic life.</t>
+  </si>
+  <si>
+    <t>This cluster represents countries that exhibit a balanced outlook, characterized by their normal stance on justifiability and a heightened sense of concern. Their strength lies in their ability to recognize and address pressing issues, reflecting a commitment to societal well-being. However, the cluster tends to exhibit a lack of confidence, which may hinder their proactive engagement and decision-making in challenging situations.</t>
+  </si>
+  <si>
+    <t>This cluster comprises countries that exhibit a cautious and analytical approach to situations, marked by a slight inclination towards justifiable actions. Their strengths lie in their ability to critically evaluate circumstances, which is enhanced by their high levels of skepticism, potentially leading to more robust decision-making. However, this cluster's weaknesses emerge from lower levels of trust and passivity, which might hinder collaboration and responsiveness to opportunities presented in their environment.</t>
+  </si>
+  <si>
+    <t>This cluster comprises countries that display a cautious and somewhat reserved disposition in their international and domestic interactions. Their specific strengths include a normal level of activity, suggesting they engage in various initiatives and projects, albeit with a hesitance stemming from their lower confidence levels. However, the cluster's weaknesses lie in their low levels of trust and confidence, which may hinder collaborative efforts and foster a sense of skepticism in crucial partnerships.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as empathetic analyst?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as justifiable skeptic?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as thoughtful observer?</t>
+  </si>
+  <si>
+    <t>Brazil presents a cautious yet reserved approach to societal dynamics, characterized by its low levels of confidence and moderate trust. The country's specific strength lies in its ability to maintain a stable baseline without falling deeply into unconfidence, which enables some level of engagement in societal issues. However, the significantly low confidence in its justice system and authorities may limit Brazil's capacity for active participation and collaboration in community initiatives. Overall, Brazil thrives in thoughtful observation but must navigate its confidence challenges to enhance collective engagement.</t>
+  </si>
+  <si>
+    <t>Kenya presents a complex landscape characterized by a strong sense of what is deemed justifiable amongst its citizens, particularly regarding ethical dilemmas like tax evasion. The country’s noteworthy strength lies in its well-grounded perspectives, highlighting a rational approach to decisions and actions. However, Kenya grapples with low trust levels, which, alongside an average skepticism, may hinder the development of cooperative relationships and a sense of community. Overall, while Kenya exhibits thoughtful evaluation, its challenges in trust and collaboration could pose limitations for its social cohesion and progress.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of Kenya: ```Kenya is extremely high on justifiable. In particular, Kenya indicates that Is 'cheating on taxes if you have a chance' can always be justified, never be justified, or something in between: (on a scale of 'never justifiable' to 'always justifiable'). Kenya is quite low on trusting. Kenya is average on skeptical. Kenya is very low on active. In particular, Kenya indicates that Are you a member of a consumer organization? (on a scale of 'are an active member' to 'don't belong'). ´´´ Here is the informative description of Kenya: ```Kenya is thoughtful evaluators with the following characteristics: This cluster can be characterized as a group of countries that often maintain a cautious and reserved perspective. Their strength lies in a strong sense of justifiability, suggesting that decisions and actions taken by these nations are well-grounded and rational. However, their elevated skepticism combined with lower levels of trust indicates a potential weakness in building cooperative relationships and fostering a sense of community, which may hinder collaboration both domestically and internationally.´´´</t>
+  </si>
+  <si>
+    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. 
+Here is the statistical description of Brazil: ```Brazil is quite low on unconfident. Brazil is average on trusting. Brazil is very low on confident. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is average on passive. ´´´ 
+Here is the informative description of Brazil: ```Brazil is thoughtful observer with the following characteristics: Members of this cluster can be described as relatively reserved and measured in their approach to societal issues. They exhibit a slight tendency away from feelings of unconfidence, indicating a stable base, but their low levels of trust suggest a cautious outlook on collaboration and relationships. However, their reduced confidence may hinder their ability to engage actively and decisively in community participation and individual initiatives.´´´</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -343,6 +248,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -695,15 +607,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1061,251 +970,123 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="88.54296875" customWidth="1"/>
-    <col min="2" max="2" width="103.7265625" customWidth="1"/>
+    <col min="1" max="1" width="70.81640625" customWidth="1"/>
+    <col min="2" max="2" width="89.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:2" ht="65" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="40" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="2" t="s">
+    </row>
+    <row r="11" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:2" ht="40" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="21.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:2" ht="150" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:2" ht="110" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="21.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="21.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="41.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="31.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="150" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="130" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/final_summary/messages_country.xlsx
+++ b/data/describe/few_shot/final_summary/messages_country.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F61F11C-81CD-4028-9D84-329B9F14C028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB08C7-40DF-4803-914A-3F0811E3C4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
     <t>What does it mean when a country is described as unconfident?</t>
   </si>
   <si>
-    <t>When a country is described as unconfident, it reflects a sense of hesitancy or doubt about its political institutions, such as a weak confidence in political parties and parliament. This feeling extends to social values, where there might be uncertainty about the implications of prioritizing personal well-being over work, indicating a lack of assurance in the nationâ€™s collective direction and decisions.</t>
-  </si>
-  <si>
     <t>What does it mean when a country is described as justifiable?</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
     <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. 
 Here is the statistical description of Brazil: ```Brazil is quite low on unconfident. Brazil is average on trusting. Brazil is very low on confident. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is average on passive. ´´´ 
 Here is the informative description of Brazil: ```Brazil is thoughtful observer with the following characteristics: Members of this cluster can be described as relatively reserved and measured in their approach to societal issues. They exhibit a slight tendency away from feelings of unconfidence, indicating a stable base, but their low levels of trust suggest a cautious outlook on collaboration and relationships. However, their reduced confidence may hinder their ability to engage actively and decisively in community participation and individual initiatives.´´´</t>
+  </si>
+  <si>
+    <t>When a country is described as unconfident, it reflects a sense of hesitancy or doubt about its political institutions, such as a weak confidence in political parties and parliament. This feeling extends to social values, where there might be uncertainty about the implications of prioritizing personal well-being over work, indicating a lack of assurance in the nation's collective direction and decisions.</t>
   </si>
 </sst>
 </file>
@@ -990,103 +990,103 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="65" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="52" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="52" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="52" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="52" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="52" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="40" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="40" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="40" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="150" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="110" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/describe/few_shot/final_summary/messages_country.xlsx
+++ b/data/describe/few_shot/final_summary/messages_country.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaca253\Documents\datomatisation\datomatisation-dev\data\describe\few_shot\final_summary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7DB08C7-40DF-4803-914A-3F0811E3C4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EC426E-04DC-4653-9A49-618C569CE5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>User</t>
   </si>
@@ -33,91 +33,83 @@
     <t>Assistant</t>
   </si>
   <si>
-    <t>What does it mean when a country is described as unconfident?</t>
+    <t>What does it mean when a country is described as cautious?</t>
+  </si>
+  <si>
+    <t>When a country is described as cautious, it suggests that there is some level of distrust or uncertainty regarding political institutions, such as political parties and parliament, reflecting a more reserved approach to governance and societal change. The country might also be hesitant about the potential benefits of placing less importance on work in the future, indicating a careful consideration of its values and priorities.</t>
   </si>
   <si>
     <t>What does it mean when a country is described as justifiable?</t>
   </si>
   <si>
-    <t>When a country is described as justifiable, it reflects a perspective where actions like stealing property, violence against others, accepting bribes, domestic abuse, and cheating on taxes are viewed through a lens of acceptability, suggesting that there are situations where these behaviors might seem reasonable or warranted. This stance encompasses a belief system that frequently justifies morally questionable actions, contributing to a broader understanding of social norms and ethics within that country.</t>
+    <t>When a country is described as justifiable, it indicates a strong belief among its people that actions typically viewed as wrong, such as stealing property, using violence, accepting bribes, or domestic abuse, can sometimes be justified. It also suggests that there are attitudes that support bending the rules, like cheating on taxes, which further highlights a complex moral landscape where justifications for actions are readily considered.</t>
   </si>
   <si>
     <t>What does it mean when a country is described as trusting?</t>
   </si>
   <si>
-    <t>When a country is described as trusting, it reflects a belief that most people can be relied upon and that there is a strong sense of confidence in both personal relationships and those across national boundaries. This trust extends beyond just individuals, highlighting the importance of faith in God and an openness to engage in political actions, such as signing electronic petitions, indicating a society that values cooperation and connection.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as concerned?</t>
-  </si>
-  <si>
-    <t>When a country is described as concerned, it means that its citizens are deeply troubled by various social issues and potential threats. They worry significantly about matters like education for future generations, the justifiability of abortion and homosexuality, and even the looming fear of civil unrest, indicating a collective anxiety about the moral and societal direction of their nation.</t>
+    <t>When a country is described as trusting, it demonstrates a belief in the goodness of people, with a strong conviction that most individuals can be trusted. This sense of trust extends to relationships with various nationalities, to those known personally, and reflects an overall faith in collective actions like signing petitions, alongside a significant role of spirituality in daily life.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as uncertain?</t>
+  </si>
+  <si>
+    <t>When a country is described as uncertain, it reflects a collective anxiety and ambivalence about significant social issues and personal well-being. Citizens may grapple with questions of morality, such as the justification for abortion and homosexuality, while also worrying about dire scenarios like civil war and their ability to provide quality education for their children; this creates an environment where doubt and hesitation are prevalent.</t>
   </si>
   <si>
     <t>What does it mean when a country is described as confident?</t>
   </si>
   <si>
-    <t>When a country is described as confident, it means that its citizens have a strong trust in their government, parliament, and civil service, feeling secure in the systems that govern their lives. This confidence extends notably to their justice system and political parties, suggesting a robust belief in the overall integrity and effectiveness of their institutions.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as skeptical?</t>
-  </si>
-  <si>
-    <t>When a country is described as skeptical, it conveys a sense of hesitation or doubt regarding certain activities and beliefs. This skepticism is reflected in the lower importance placed on leisure time and a reluctance toward participating in actions like signing petitions, suggesting a general caution or disbelief in the effectiveness or value of such engagements.</t>
+    <t>When a country is described as confident, it reflects a strong belief in its governmental institutions and civil services, showcasing a significant trust in the government, parliament, and the justice system. This confidence not only demonstrates faith in political stability and transparency but also reveals a collective sense of assurance among its citizens about their political and legal frameworks.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as leisure?</t>
+  </si>
+  <si>
+    <t>When a country is described as leisure, it suggests that leisure time holds some importance for its people, albeit to a lesser degree. Additionally, there may be a casual attitude towards activities like signing petitions, indicating that engagement in such civic matters is not a top priority.</t>
   </si>
   <si>
     <t>What does it mean when a country is described as active?</t>
   </si>
   <si>
-    <t>When a country is described as active, it means that its citizens are significantly engaged in professional, charitable, and consumer organizations, showing a commitment to community and collaboration. This vibrant participation reflects a society that values involvement and cooperation, often leading to a diverse range of initiatives that enhance social ties and support among individuals.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as passive?</t>
-  </si>
-  <si>
-    <t>When a country is described as passive, it suggests a tendency to shy away from active participation in political engagement, such as signing electronic petitions or taking community initiatives. This passivity reflects a reluctance to engage in actions that drive societal change, indicating a more subdued presence in active civic life.</t>
-  </si>
-  <si>
-    <t>This cluster represents countries that exhibit a balanced outlook, characterized by their normal stance on justifiability and a heightened sense of concern. Their strength lies in their ability to recognize and address pressing issues, reflecting a commitment to societal well-being. However, the cluster tends to exhibit a lack of confidence, which may hinder their proactive engagement and decision-making in challenging situations.</t>
-  </si>
-  <si>
-    <t>This cluster comprises countries that exhibit a cautious and analytical approach to situations, marked by a slight inclination towards justifiable actions. Their strengths lie in their ability to critically evaluate circumstances, which is enhanced by their high levels of skepticism, potentially leading to more robust decision-making. However, this cluster's weaknesses emerge from lower levels of trust and passivity, which might hinder collaboration and responsiveness to opportunities presented in their environment.</t>
-  </si>
-  <si>
-    <t>This cluster comprises countries that display a cautious and somewhat reserved disposition in their international and domestic interactions. Their specific strengths include a normal level of activity, suggesting they engage in various initiatives and projects, albeit with a hesitance stemming from their lower confidence levels. However, the cluster's weaknesses lie in their low levels of trust and confidence, which may hinder collaborative efforts and foster a sense of skepticism in crucial partnerships.</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as empathetic analyst?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as justifiable skeptic?</t>
-  </si>
-  <si>
-    <t>What does it mean when a country is described as thoughtful observer?</t>
-  </si>
-  <si>
-    <t>Brazil presents a cautious yet reserved approach to societal dynamics, characterized by its low levels of confidence and moderate trust. The country's specific strength lies in its ability to maintain a stable baseline without falling deeply into unconfidence, which enables some level of engagement in societal issues. However, the significantly low confidence in its justice system and authorities may limit Brazil's capacity for active participation and collaboration in community initiatives. Overall, Brazil thrives in thoughtful observation but must navigate its confidence challenges to enhance collective engagement.</t>
-  </si>
-  <si>
-    <t>Kenya presents a complex landscape characterized by a strong sense of what is deemed justifiable amongst its citizens, particularly regarding ethical dilemmas like tax evasion. The country’s noteworthy strength lies in its well-grounded perspectives, highlighting a rational approach to decisions and actions. However, Kenya grapples with low trust levels, which, alongside an average skepticism, may hinder the development of cooperative relationships and a sense of community. Overall, while Kenya exhibits thoughtful evaluation, its challenges in trust and collaboration could pose limitations for its social cohesion and progress.</t>
-  </si>
-  <si>
-    <t>Here is the statistical description of Kenya: ```Kenya is extremely high on justifiable. In particular, Kenya indicates that Is 'cheating on taxes if you have a chance' can always be justified, never be justified, or something in between: (on a scale of 'never justifiable' to 'always justifiable'). Kenya is quite low on trusting. Kenya is average on skeptical. Kenya is very low on active. In particular, Kenya indicates that Are you a member of a consumer organization? (on a scale of 'are an active member' to 'don't belong'). ´´´ Here is the informative description of Kenya: ```Kenya is thoughtful evaluators with the following characteristics: This cluster can be characterized as a group of countries that often maintain a cautious and reserved perspective. Their strength lies in a strong sense of justifiability, suggesting that decisions and actions taken by these nations are well-grounded and rational. However, their elevated skepticism combined with lower levels of trust indicates a potential weakness in building cooperative relationships and fostering a sense of community, which may hinder collaboration both domestically and internationally.´´´</t>
-  </si>
-  <si>
-    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. 
-Here is the statistical description of Brazil: ```Brazil is quite low on unconfident. Brazil is average on trusting. Brazil is very low on confident. In particular, Brazil indicates that How much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all'). Brazil is average on passive. ´´´ 
-Here is the informative description of Brazil: ```Brazil is thoughtful observer with the following characteristics: Members of this cluster can be described as relatively reserved and measured in their approach to societal issues. They exhibit a slight tendency away from feelings of unconfidence, indicating a stable base, but their low levels of trust suggest a cautious outlook on collaboration and relationships. However, their reduced confidence may hinder their ability to engage actively and decisively in community participation and individual initiatives.´´´</t>
-  </si>
-  <si>
-    <t>When a country is described as unconfident, it reflects a sense of hesitancy or doubt about its political institutions, such as a weak confidence in political parties and parliament. This feeling extends to social values, where there might be uncertainty about the implications of prioritizing personal well-being over work, indicating a lack of assurance in the nation's collective direction and decisions.</t>
+    <t>When a country is described as active, it means that its citizens are deeply engaged in various professional and charitable organizations, showcasing a strong commitment to community and collaborative efforts. With members actively participating in mutual aid groups and consumer organizations, this vibrant society fosters trust and connection among its people, signifying a robust involvement in shaping their collective future.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as disengaged?</t>
+  </si>
+  <si>
+    <t>A country described as disengaged tends to show a lack of involvement in community and social initiatives, as indicated by a generally low inclination to participate in political actions like signing electronic petitions. This disengagement reflects a broader disconnection from civic responsibilities and communal activities that help shape society.</t>
+  </si>
+  <si>
+    <t>These countries that exhibit a generally open approach to their affairs, marked by a relative lack of caution and trust. Their strengths lie in their normal levels of activity, which suggests they are not stagnant and may engage in various initiatives. However, the cluster's weaknesses include a significant absence of confidence and trusting behaviors, potentially leading to challenges in collaboration and decision-making.</t>
+  </si>
+  <si>
+    <t>These countries can be described as highly justifiable in their actions and decisions, showcasing a strong sense of rationale. Their balanced levels of trust and confidence indicate a conducive environment for cooperation and stability among citizens. However, their relatively low activity levels suggest a potential disengagement from proactive initiatives, which may hinder progress and development.</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as open initiative?</t>
+  </si>
+  <si>
+    <t>What does it mean when a country is described as rational stability?</t>
+  </si>
+  <si>
+    <t>Fantastic! That’s exactly what I needed. Now, let’s return to your analysis. Your next task is to describe a specific country based on the provided information. Please use the statistical description enclosed with ``` ´´´ to give a concise, four sentence summary of the country. The first sentence should use varied language to give an overview of the country. The second sentence should describe the country's specific strengths based on the metrics. The third sentence should describe aspects in which the country is average and/or weak based on the statistics. Finally, summarize the country with a single concluding statement. Here is the statistical description of Brazil: ```Brazil is quite low on cautious. Brazil is average on trusting. Brazil is very low on confident. In particular, Brazil has characteristics related to 'how much confidence do you have in the justice system/courts? (on a scale of ' a great deal' to 'none at all')'. Brazil is average on disengaged. ´´´ Here is the informative description of Brazil: ```Brazil is open initiative with the following characteristics: This cluster represents countries that exhibit a generally open approach to their affairs, marked by a relative lack of caution and trust. Their strengths lie in their normal levels of activity, which suggests they are not stagnant and may engage in various initiatives. However, the cluster's weaknesses include a significant absence of confidence and trusting behaviors, potentially leading to challenges in collaboration and decision-making.´´´</t>
+  </si>
+  <si>
+    <t>Brazil presents itself as a country with a notably open initiative, characterized by its relative lack of caution and a moderate level of trust. Its strength lies in an active engagement with various initiatives, indicating a dynamic approach to societal issues. However, Brazil exhibits very low confidence, particularly in its justice system, which may pose challenges to collaborative efforts and effective decision-making. Overall, Brazil's unique blend of openness and activity highlights both its potential for innovation and the hurdles it faces due to a lack of trust.</t>
+  </si>
+  <si>
+    <t>Here is the statistical description of Greece: ```Greece is very low on cautious. In particular, Greece has characteristics related to 'in the future, would it be a good thing if less importance is placed on work? (on a scale of 'good' to 'bad')'. Greece is average on uncertain. Greece is quite low on confident. Greece is quite high on disengaged. ´´´ Here is the informative description of Greece: ```Greece is open initiative with the following characteristics: This cluster represents countries that exhibit a generally open approach to their affairs, marked by a relative lack of caution and trust. Their strengths lie in their normal levels of activity, which suggests they are not stagnant and may engage in various initiatives. However, the cluster's weaknesses include a significant absence of confidence and trusting behaviors, potentially leading to challenges in collaboration and decision-making.´´</t>
+  </si>
+  <si>
+    <t>Greece presents a unique landscape characterized by its open initiative toward social and economic affairs. The country exhibits a notable strength in its willingness to engage in various initiatives, reflecting a vibrant social dynamic. However, Greece's significant lack of caution and lower confidence levels may hinder collaborative efforts and effective decision-making. In summary, Greece's openness may result in active engagement, but it also poses challenges due to its cautiousness and confidence deficits.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,19 +243,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -607,12 +586,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -970,11 +946,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="70.81640625" customWidth="1"/>
-    <col min="2" max="2" width="89.81640625" customWidth="1"/>
+    <col min="1" max="1" width="77.54296875" customWidth="1"/>
+    <col min="2" max="2" width="78.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -985,108 +961,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="65" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="52" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="39" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="40" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="150" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="110" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
+    <row r="13" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
